--- a/ig/DM-37/CodeSystem-TRE-R302-ContexteCodeComplementaire.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R302-ContexteCodeComplementaire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>Autre</t>
+  </si>
+  <si>
+    <t>Tout ce qui n'est pas listé de façon exhaustive dans la liste de codes</t>
   </si>
   <si>
     <t>AUT</t>
@@ -606,17 +609,19 @@
       <c r="C3" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -625,10 +630,10 @@
         <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -637,10 +642,10 @@
         <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2"/>
     </row>
